--- a/test_samples/DSV/sample2_ref.xlsx
+++ b/test_samples/DSV/sample2_ref.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\LC\供應商帳單\DSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼供應商帳單\DSV____________OK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C503C7-8657-4504-A7E4-1D2483866525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28275858-68F9-41B1-99CB-76AAC46CB5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
+    <workbookView xWindow="3210" yWindow="6090" windowWidth="28800" windowHeight="15315" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
   </bookViews>
   <sheets>
     <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="43">
   <si>
     <t>INVOICE DATE
 發票日期</t>
@@ -196,6 +196,15 @@
   </si>
   <si>
     <t>ID610413181</t>
+  </si>
+  <si>
+    <t>Shipper
+出貨方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -261,7 +270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -278,9 +287,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -617,27 +623,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF1381F-552A-4924-9A7A-4C0080F73CE6}">
-  <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:R21"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" customWidth="1"/>
-    <col min="3" max="3" width="29.453125" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="3" max="3" width="29.5" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" customWidth="1"/>
-    <col min="7" max="7" width="29.26953125" customWidth="1"/>
-    <col min="8" max="9" width="13.7265625" customWidth="1"/>
-    <col min="10" max="10" width="20.54296875" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="16.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.36328125" customWidth="1"/>
-    <col min="15" max="15" width="20.6328125" customWidth="1"/>
-    <col min="16" max="16" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="29.25" customWidth="1"/>
+    <col min="9" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="20.5" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.375" customWidth="1"/>
+    <col min="16" max="16" width="20.625" customWidth="1"/>
+    <col min="17" max="17" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -657,37 +663,43 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R1" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>46268</v>
       </c>
@@ -706,38 +718,44 @@
       <c r="F2" s="4">
         <v>3140183</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4">
+        <v>345420</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="3">
-        <v>46311</v>
-      </c>
       <c r="I2" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J2" s="3">
+        <v>46269</v>
       </c>
       <c r="K2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="4">
+        <v>25</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="4">
         <v>8.4710000000000001</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46268</v>
       </c>
@@ -756,38 +774,44 @@
       <c r="F3" s="4">
         <v>546601</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4">
+        <v>60126</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="3">
-        <v>46311</v>
-      </c>
       <c r="I3" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J3" s="3">
+        <v>46269</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="4">
+        <v>25</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="4">
         <v>8.4710000000000001</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>46268</v>
       </c>
@@ -806,38 +830,44 @@
       <c r="F4" s="4">
         <v>169309</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4">
+        <v>18624</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="3">
-        <v>46311</v>
-      </c>
       <c r="I4" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J4" s="3">
+        <v>46269</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="4">
+        <v>25</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4">
         <v>8.4710000000000001</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46268</v>
       </c>
@@ -856,38 +886,44 @@
       <c r="F5" s="4">
         <v>622000</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4">
+        <v>68420</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="3">
-        <v>46311</v>
-      </c>
       <c r="I5" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J5" s="3">
+        <v>46269</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="4">
+        <v>25</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="4">
         <v>8.4710000000000001</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="Q5" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>46268</v>
       </c>
@@ -906,38 +942,44 @@
       <c r="F6" s="4">
         <v>2945566</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4">
+        <v>324012</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="3">
-        <v>46311</v>
-      </c>
       <c r="I6" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J6" s="3">
+        <v>46269</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="4">
+        <v>25</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="4">
         <v>7.9459999999999997</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="P6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="Q6" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>46268</v>
       </c>
@@ -956,38 +998,44 @@
       <c r="F7" s="4">
         <v>546601</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4">
+        <v>60126</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="3">
-        <v>46311</v>
-      </c>
       <c r="I7" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J7" s="3">
+        <v>46269</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="4">
+        <v>25</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="4">
         <v>7.9459999999999997</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>46268</v>
       </c>
@@ -1006,38 +1054,44 @@
       <c r="F8" s="4">
         <v>169309</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4">
+        <v>18624</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="3">
-        <v>46311</v>
-      </c>
       <c r="I8" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J8" s="3">
+        <v>46269</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="4">
+        <v>25</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="4">
         <v>7.9459999999999997</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="P8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="Q8" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>46268</v>
       </c>
@@ -1056,38 +1110,44 @@
       <c r="F9" s="4">
         <v>583451</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4">
+        <v>64180</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="3">
-        <v>46311</v>
-      </c>
       <c r="I9" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46269</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="4">
+        <v>25</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="4">
         <v>7.9459999999999997</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="P9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="Q9" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>46268</v>
       </c>
@@ -1106,38 +1166,44 @@
       <c r="F10" s="4">
         <v>19526146</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4">
+        <v>2147876</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="3">
-        <v>46311</v>
-      </c>
       <c r="I10" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J10" s="3">
+        <v>46269</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="4">
+        <v>25</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="4">
         <v>52.673999999999999</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="P10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="Q10" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>46268</v>
       </c>
@@ -1156,38 +1222,44 @@
       <c r="F11" s="4">
         <v>546601</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4">
+        <v>60126</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="3">
-        <v>46311</v>
-      </c>
       <c r="I11" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J11" s="3">
+        <v>46269</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="4">
+        <v>25</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="4">
         <v>52.673999999999999</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>46268</v>
       </c>
@@ -1206,39 +1278,44 @@
       <c r="F12" s="4">
         <v>169309</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4">
+        <v>18624</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="3">
-        <v>46311</v>
-      </c>
       <c r="I12" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J12" s="3">
+        <v>46269</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N12" s="4">
+        <v>25</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="4">
         <v>52.673999999999999</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="P12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P12" s="4" t="s">
+      <c r="Q12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="Q12" s="6"/>
-    </row>
-    <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>46268</v>
       </c>
@@ -1257,38 +1334,44 @@
       <c r="F13" s="4">
         <v>3867694</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4">
+        <v>425446</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="3">
-        <v>46311</v>
-      </c>
       <c r="I13" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J13" s="3">
+        <v>46269</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="4">
+        <v>25</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="4">
         <v>52.673999999999999</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="P13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P13" s="4" t="s">
+      <c r="Q13" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="R13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>46268</v>
       </c>
@@ -1307,38 +1390,41 @@
       <c r="F14" s="4">
         <v>4565517</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4">
+        <v>502207</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="3">
-        <v>46311</v>
-      </c>
       <c r="I14" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J14" s="3">
+        <v>46269</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N14" s="4">
+        <v>25</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="4">
         <v>12.316000000000001</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="P14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="Q14" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>46268</v>
       </c>
@@ -1357,38 +1443,41 @@
       <c r="F15" s="4">
         <v>546601</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="4">
+        <v>60126</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="3">
-        <v>46311</v>
-      </c>
       <c r="I15" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J15" s="3">
+        <v>46269</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N15" s="4">
+        <v>25</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="4">
         <v>12.316000000000001</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="P15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P15" s="4" t="s">
+      <c r="Q15" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>46268</v>
       </c>
@@ -1407,38 +1496,41 @@
       <c r="F16" s="4">
         <v>169309</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4">
+        <v>18624</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="3">
-        <v>46311</v>
-      </c>
       <c r="I16" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J16" s="3">
+        <v>46269</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="4">
+        <v>25</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" s="4">
         <v>12.316000000000001</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="P16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P16" s="4" t="s">
+      <c r="Q16" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>46268</v>
       </c>
@@ -1457,38 +1549,41 @@
       <c r="F17" s="4">
         <v>904327</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4">
+        <v>99476</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="3">
-        <v>46311</v>
-      </c>
       <c r="I17" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J17" s="3">
+        <v>46269</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N17" s="4">
+        <v>25</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" s="4">
         <v>12.316000000000001</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="P17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P17" s="4" t="s">
+      <c r="Q17" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>46268</v>
       </c>
@@ -1507,38 +1602,41 @@
       <c r="F18" s="4">
         <v>5981212</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4">
+        <v>657933</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H18" s="3">
-        <v>46311</v>
-      </c>
       <c r="I18" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J18" s="3">
+        <v>46269</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N18" s="4">
+        <v>25</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="4">
         <v>16.135000000000002</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="P18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P18" s="4" t="s">
+      <c r="Q18" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>46268</v>
       </c>
@@ -1557,38 +1655,41 @@
       <c r="F19" s="4">
         <v>546601</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="4">
+        <v>60126</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H19" s="3">
-        <v>46311</v>
-      </c>
       <c r="I19" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J19" s="3">
+        <v>46269</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N19" s="4">
+        <v>25</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19" s="4">
         <v>16.135000000000002</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="P19" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P19" s="4" t="s">
+      <c r="Q19" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>46268</v>
       </c>
@@ -1607,38 +1708,41 @@
       <c r="F20" s="4">
         <v>169309</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4">
+        <v>18624</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H20" s="3">
-        <v>46311</v>
-      </c>
       <c r="I20" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J20" s="3">
+        <v>46269</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N20" s="4">
+        <v>25</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="4">
         <v>16.135000000000002</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="P20" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P20" s="4" t="s">
+      <c r="Q20" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>46268</v>
       </c>
@@ -1657,34 +1761,37 @@
       <c r="F21" s="4">
         <v>1184745</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4">
+        <v>130322</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H21" s="3">
-        <v>46311</v>
-      </c>
       <c r="I21" s="3">
-        <v>46269</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>24</v>
+        <v>46311</v>
+      </c>
+      <c r="J21" s="3">
+        <v>46269</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N21" s="4">
+        <v>25</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="4">
         <v>16.135000000000002</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="P21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="P21" s="4" t="s">
+      <c r="Q21" s="4" t="s">
         <v>33</v>
       </c>
     </row>
